--- a/Ethanol-Water-Material-Balance/Ethanol-Water-Material-Balance-Model.xlsx
+++ b/Ethanol-Water-Material-Balance/Ethanol-Water-Material-Balance-Model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3AF6BDB6FD02CC28/Documents/GitHub/ChemEProjects/Ethanol Water Material Balance Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3AF6BDB6FD02CC28/Documents/GitHub/ChemEProjects/Ethanol-Water-Material-Balance/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="882" documentId="8_{66A1A9FC-005E-44AA-8839-2039AE58A330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F977AE64-87B6-4BB8-A3D5-99A62C9E0A1C}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="13920" yWindow="258" windowWidth="3456" windowHeight="1746" activeTab="1" xr2:uid="{F31F3049-9973-4664-9FE7-54287E385AA7}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{F31F3049-9973-4664-9FE7-54287E385AA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Single-Pass Recycle Model" sheetId="1" r:id="rId1"/>
